--- a/_final_project/2026F/rubric/Predictive_Analytics_Poster_Rubric.xlsx
+++ b/_final_project/2026F/rubric/Predictive_Analytics_Poster_Rubric.xlsx
@@ -1,183 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rubric" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rubric" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Criterion</t>
-  </si>
-  <si>
-    <t>Points</t>
-  </si>
-  <si>
-    <t>Exemplary (Full Points)</t>
-  </si>
-  <si>
-    <t>Competent (Partial Points)</t>
-  </si>
-  <si>
-    <t>Needs Improvement (Minimal Points)</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Prediction Goal(s)</t>
-  </si>
-  <si>
-    <t>Dataset Overview</t>
-  </si>
-  <si>
-    <t>Exploratory Data Analysis (EDA)</t>
-  </si>
-  <si>
-    <t>Data Preparation (Merged: Feature Engineering + Missing Data)</t>
-  </si>
-  <si>
-    <t>Baseline Model (Choice, CV, Interpretation)</t>
-  </si>
-  <si>
-    <t>More Complex Model (Choice, Tuning, Comparison)</t>
-  </si>
-  <si>
-    <t>Report Quality &amp; Visual Communication</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>5 pts: Clear, specific predictive objective(s); response type (regression/classification) explicitly identified and justified; strong business/research rationale.</t>
-  </si>
-  <si>
-    <t>7–8 pts: Reports #obs/#features; types for key features; response variable identified/typed; data provenance/window stated.</t>
-  </si>
-  <si>
-    <t>10–12 pts: Appropriate summaries (response + key predictors); ≥2 relevant plots; interprets skew/outliers/imbalance/seasonality; connects insights to modeling choices and metric selection.</t>
-  </si>
-  <si>
-    <t>17–20 pts: ≥1 non-trivial new feature (interactions, lags/rolling stats, domain-driven ratios, text-derived signals) with clear rationale; quantifies missingness by feature; justified strategy (drop/impute/advanced) with leakage-safe implementation; demonstrates impact via ablation/CV deltas or sensitivity to imputation choices.</t>
-  </si>
-  <si>
-    <t>17–20 pts: Appropriate simple baseline (e.g., Linear/Logistic Regression); pipeline is leakage-safe; k=5/10 CV with correct metric (RMSE/MAE/Accuracy/F1/AUC); tracks mean/variance; summarizes implications and limitations; proposes concrete next steps.</t>
-  </si>
-  <si>
-    <t>22–25 pts: Model aligned to data/goal (RF/GBM/XGBoost/SVM/regularized GLM/NN); hyperparameter search (grid/random/Bayesian) inside proper CV; leakage controls (scaling/encoding inside folds); comparative results (tables/plots) with variability and selection criterion; rigorous comparison to baseline with practical interpretation (effect sizes, trade-offs), plus error/confusion analysis where relevant.</t>
-  </si>
-  <si>
-    <t>9–10 pts: Clear, scannable poster; logical flow (Intro→Methods→Results→Conclusions); legible, labeled figures/tables (titles, axes, units, legends); consistent typography/layout; code refs/appendix where appropriate; minimal grammar issues.</t>
-  </si>
-  <si>
-    <t>3–4 pts: Goal stated; response type identified but weakly justified; limited link to context.</t>
-  </si>
-  <si>
-    <t>4–6 pts: Size and response identified; partial feature typing; minimal provenance.</t>
-  </si>
-  <si>
-    <t>6–9 pts: Basic stats and ≥1 plot; some interpretation but limited linkage to modeling.</t>
-  </si>
-  <si>
-    <t>10–16 pts: New feature with partial rationale; identifies missingness and applies a reasonable method; limited evidence of impact or sensitivity analysis.</t>
-  </si>
-  <si>
-    <t>10–16 pts: Reasonable model; CV present with partial integration/details; metric adequate; interpretation limited or generic.</t>
-  </si>
-  <si>
-    <t>13–21 pts: Plausible model; some tuning with partial documentation; CV present but thin; basic comparison to baseline; limited practical takeaways.</t>
-  </si>
-  <si>
-    <t>6–8 pts: Generally readable; minor layout/labeling gaps; some figures under-explained or styling inconsistencies.</t>
-  </si>
-  <si>
-    <t>0–2 pts: Goal unclear/missing; response type unspecified; no rationale.</t>
-  </si>
-  <si>
-    <t>0–3 pts: Missing size/response ID; little/no feature typing or context.</t>
-  </si>
-  <si>
-    <t>0–5 pts: Incomplete stats; weak/irrelevant visuals; minimal/no interpretation.</t>
-  </si>
-  <si>
-    <t>0–9 pts: No new/trivial feature; missingness unreported or mishandled; unjustified/inappropriate method; no evidence of value.</t>
-  </si>
-  <si>
-    <t>0–9 pts: Inappropriate/unspecified baseline; no/incorrect CV; unclear metric; raw numbers only; no reflection.</t>
-  </si>
-  <si>
-    <t>0–12 pts: Misaligned/unspecified model; superficial/absent tuning; incorrect CV; opaque selection; no clear comparison or interpretation.</t>
-  </si>
-  <si>
-    <t>0–5 pts: Disorganized; illegible/unlabeled visuals; weak linkage between text and graphics; notable grammar/formatting issues.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -211,16 +69,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -508,174 +433,285 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="63.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="6" width="80.7109375" customWidth="1"/>
+    <col width="3.7109375" customWidth="1" min="1" max="1"/>
+    <col width="63.7109375" customWidth="1" min="2" max="2"/>
+    <col width="8.7109375" customWidth="1" min="3" max="3"/>
+    <col width="80.7109375" customWidth="1" min="4" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Exemplary (Full Points)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Competent (Partial Points)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Needs Improvement (Minimal Points)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Prediction Goal(s)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5 pts: Clear, specific predictive objective(s); response type (regression/classification) explicitly identified and justified; strong business/research rationale.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3–4 pts: Goal stated; response type identified but weakly justified; limited link to context.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0–2 pts: Goal unclear/missing; response type unspecified; no rationale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dataset Overview</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7–8 pts: Reports #obs/#features; types for key features; response variable identified/typed; data provenance/window stated.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4–6 pts: Size and response identified; partial feature typing; minimal provenance.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0–3 pts: Missing size/response ID; little/no feature typing or context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Exploratory Data Analysis (EDA)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10–12 pts: Appropriate summaries (response + key predictors); ≥2 relevant plots; interprets skew/outliers/imbalance/seasonality; connects insights to modeling choices and metric selection.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6–9 pts: Basic stats and ≥1 plot; some interpretation but limited linkage to modeling.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0–5 pts: Incomplete stats; weak/irrelevant visuals; minimal/no interpretation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Data Preparation (Feature Engineering, Missing Data, etc.)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>15–18 pts: ≥1 non-trivial new feature (interactions, lags/rolling stats, domain-driven ratios, text-derived signals) with clear rationale; quantifies missingness by feature; justified strategy (drop/impute/advanced) with leakage-safe implementation; demonstrates impact via ablation/CV deltas or sensitivity to imputation choices.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>9–14 pts: New feature with partial rationale; identifies missingness and applies a reasonable method; limited evidence of impact or sensitivity analysis.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0–8 pts: No new/trivial feature; missingness unreported or mishandled; unjustified/inappropriate method; no evidence of value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Baseline Model (Choice, CV, Interpretation)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>14–17 pts: Appropriate simple baseline (e.g., Linear/Logistic Regression); pipeline is leakage-safe; k=5/10 CV with correct metric (RMSE/MAE/Accuracy/F1/AUC); tracks mean/variance; summarizes implications and limitations; proposes concrete next steps.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8–13 pts: Reasonable model; CV present with partial integration/details; metric adequate; interpretation limited or generic.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0–7 pts: Inappropriate/unspecified baseline; no/incorrect CV; unclear metric; raw numbers only; no reflection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>More Complex Model (Choice, Tuning, Paired Comparison)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>22–25 pts: Model aligned to data/goal (RF/GBM/XGBoost/SVM/regularized GLM/NN); hyperparameter search (grid/random/Bayesian) inside proper CV; leakage controls (scaling/encoding inside folds); compared with the baseline on identical folds (same splitter and seed) using per-fold paired differences, against a practical margin stated before the results; mean paired difference reported with an approximate 95% interval labeled descriptive; verdict names the correct outcome: real difference (every fold favors the same model and the gap clears the margin), inconclusive (the sign changes across folds), or practically equivalent (same sign but under the margin, so the simpler model wins); practical interpretation (effect sizes, trade-offs), plus error/confusion analysis where relevant.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>13–21 pts: Plausible model; some tuning with partial documentation; CV present but thin; compares with the baseline on CV means or side-by-side intervals rather than paired per-fold differences, judges a winner or a tie by whether intervals overlap, or states no margin; limited practical takeaways.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0–12 pts: Misaligned/unspecified model; superficial/absent tuning; incorrect CV; opaque selection; no clear comparison or interpretation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Report Quality &amp; Visual Communication</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>9–10 pts: Clear, scannable poster; logical flow (Intro→Methods→Results→Conclusions); legible, labeled figures/tables (titles, axes, units, legends); consistent typography/layout; code refs/appendix where appropriate; minimal grammar issues.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>6–8 pts: Generally readable; minor layout/labeling gaps; some figures under-explained or styling inconsistencies.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0–5 pts: Disorganized; illegible/unlabeled visuals; weak linkage between text and graphics; notable grammar/formatting issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" t="s">
-        <v>45</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sources, Acknowledgments, AI Use &amp; Data Privacy</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5 pts: Data source cited (provider, URL or DOI, version or access date); references support the business-problem claims and the main software is credited (e.g., scikit-learn, pandas); Acknowledgments section names the Mitch Daniels School of Business, Prof. Moreira, the TAs, and other contributors; AI Use Disclosure names each AI tool and what it was used for and states that the team verified the output (or states that no AI tools were used); only aggregated or anonymized data and examples.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3–4 pts: AI Use Disclosure present but vague (names tools without saying what they did), or one other element missing or incomplete (e.g., acknowledgments omit the TAs; data source cited without references or tools). No privacy issue.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0–2 pts: No AI Use Disclosure, or two or more other elements missing. Any personally identifiable or NDA-restricted data on the poster scores 0 here and must be removed before printing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>SUM(C2:C9)</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/_final_project/2026F/rubric/Predictive_Analytics_Poster_Rubric.xlsx
+++ b/_final_project/2026F/rubric/Predictive_Analytics_Poster_Rubric.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22–25 pts: Model aligned to data/goal (RF/GBM/XGBoost/SVM/regularized GLM/NN); hyperparameter search (grid/random/Bayesian) inside proper CV; leakage controls (scaling/encoding inside folds); compared with the baseline on identical folds (same splitter and seed) using per-fold paired differences, against a practical margin stated before the results; mean paired difference reported with an approximate 95% interval labeled descriptive; verdict names the correct outcome: real difference (every fold favors the same model and the gap clears the margin), inconclusive (the sign changes across folds), or practically equivalent (same sign but under the margin, so the simpler model wins); practical interpretation (effect sizes, trade-offs), plus error/confusion analysis where relevant.</t>
+          <t>22–25 pts: Model aligned to data/goal (RF/GBM/XGBoost/SVM/regularized GLM/NN); hyperparameter search (grid/random/Bayesian) inside proper CV; leakage controls (scaling/encoding inside folds); compared with the baseline on identical folds (same splitter and seed) using per-fold paired differences, signed so a positive value favors the complex model, against a practical margin stated before the results; mean paired difference reported with an approximate 95% interval corrected for fold overlap (mean ± t × SD of the differences × √(1/k + 1/(k−1))); verdict names the correct outcome: worthwhile gain (the whole interval lies above the margin: adopt the complex model), worthwhile loss (the whole interval lies below minus the margin: keep the baseline), practically equivalent (the whole interval lies inside ± the margin, so the simpler model wins), or unresolved (anything else: the simpler model is kept as a stated policy, not called equivalent); fold-by-fold wins reported as description, not as the verdict; practical interpretation (effect sizes, trade-offs), plus error/confusion analysis where relevant.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13–21 pts: Plausible model; some tuning with partial documentation; CV present but thin; compares with the baseline on CV means or side-by-side intervals rather than paired per-fold differences, judges a winner or a tie by whether intervals overlap, or states no margin; limited practical takeaways.</t>
+          <t>13–21 pts: Plausible model; some tuning with partial documentation; CV present but thin; compares with the baseline on CV means or side-by-side intervals rather than paired per-fold differences; judges a winner or a tie by whether intervals overlap or by fold signs alone; calls the models equivalent when the interval extends past the margin; or states no margin; limited practical takeaways.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/_final_project/2026F/rubric/Predictive_Analytics_Poster_Rubric.xlsx
+++ b/_final_project/2026F/rubric/Predictive_Analytics_Poster_Rubric.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22–25 pts: Model aligned to data/goal (RF/GBM/XGBoost/SVM/regularized GLM/NN); hyperparameter search (grid/random/Bayesian) inside proper CV; leakage controls (scaling/encoding inside folds); compared with the baseline on identical folds (same splitter and seed) using per-fold paired differences, signed so a positive value favors the complex model, against a practical margin stated before the results; mean paired difference reported with an approximate 95% interval corrected for fold overlap (mean ± t × SD of the differences × √(1/k + 1/(k−1))); verdict names the correct outcome: worthwhile gain (the whole interval lies above the margin: adopt the complex model), worthwhile loss (the whole interval lies below minus the margin: keep the baseline), practically equivalent (the whole interval lies inside ± the margin, so the simpler model wins), or unresolved (anything else: the simpler model is kept as a stated policy, not called equivalent); fold-by-fold wins reported as description, not as the verdict; practical interpretation (effect sizes, trade-offs), plus error/confusion analysis where relevant.</t>
+          <t>22–25 pts: Model aligned to data/goal (RF/GBM/XGBoost/SVM/regularized GLM/NN); hyperparameter search (grid/random/Bayesian) inside proper CV; leakage controls (scaling/encoding inside folds); compared with the baseline on identical folds (same splitter and seed) using per-fold paired differences (positive favors the complex model) against a margin stated before the results; mean difference reported with an approximate 95% interval corrected for fold overlap: mean ± t × SD(differences) × √(1/k + 1/(k−1)); verdict names the outcome: worthwhile gain (interval entirely above the margin), worthwhile loss (entirely below minus the margin), practically equivalent (entirely inside ± the margin: the simpler model wins), or unresolved (anything else: the simpler model stays as a stated policy, not called equivalent); practical interpretation (effect sizes, trade-offs), plus error/confusion analysis where relevant.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/_final_project/2026F/rubric/Predictive_Analytics_Poster_Rubric.xlsx
+++ b/_final_project/2026F/rubric/Predictive_Analytics_Poster_Rubric.xlsx
@@ -493,17 +493,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5 pts: Clear, specific predictive objective(s); response type (regression/classification) explicitly identified and justified; strong business/research rationale.</t>
+          <t>5 pts: Clear, specific predictive objective(s); response type (regression/classification) explicitly identified and justified; names the stakeholder and the decision the predictions support; strong business/research rationale.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3–4 pts: Goal stated; response type identified but weakly justified; limited link to context.</t>
+          <t>3–4 pts: Goal and response type stated, but the stakeholder, the decision, or the rationale is thin; limited link to context.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0–2 pts: Goal unclear/missing; response type unspecified; no rationale.</t>
+          <t>0–2 pts: Goal unclear/missing; response type unspecified; no link to a stakeholder's decision.</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>14–17 pts: Appropriate simple baseline (e.g., Linear/Logistic Regression); pipeline is leakage-safe; k=5/10 CV with correct metric (RMSE/MAE/Accuracy/F1/AUC); tracks mean/variance; summarizes implications and limitations; proposes concrete next steps.</t>
+          <t>14–17 pts: Appropriate simple baseline (e.g., Linear/Logistic Regression), the incumbent any complex model must beat; pipeline is leakage-safe; k=5/10 CV (time-respecting for forecasting) with a primary metric chosen for the cost of errors; reports the fold scores with their mean and SD (no per-model confidence interval needed); summarizes implications and limitations; proposes concrete next steps.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>More Complex Model (Choice, Tuning, Paired Comparison)</t>
+          <t>Model Comparison and Champion Selection (Choice, Tuning, Paired Comparison, Rationale)</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -633,17 +633,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22–25 pts: Model aligned to data/goal (RF/GBM/XGBoost/SVM/regularized GLM/NN); hyperparameter search (grid/random/Bayesian) inside proper CV; leakage controls (scaling/encoding inside folds); compared with the baseline on identical folds (same splitter and seed) using per-fold paired differences (positive favors the complex model) against a margin stated before the results; mean difference reported with an approximate 95% interval corrected for fold overlap: mean ± t × SD(differences) × √(1/k + 1/(k−1)); verdict names the outcome: worthwhile gain (interval entirely above the margin), worthwhile loss (entirely below minus the margin), practically equivalent (entirely inside ± the margin: the simpler model wins), or unresolved (anything else: the simpler model stays as a stated policy, not called equivalent); practical interpretation (effect sizes, trade-offs), plus error/confusion analysis where relevant.</t>
+          <t>22–25 pts: Model aligned to data/goal (e.g., RF/GBM/SVM/NN); tuning inside CV with leakage controls. Before comparing: primary metric, margin δ (smallest gain that would change the stakeholder's decision, with its business meaning), and candidate order (simplest first). Identical folds; per-fold differences (positive favors the challenger); interval corrected for fold overlap: mean ± t × SD(differences) × √(1/k + 1/(k−1)); outcome named: worthwhile gain (entirely above δ), worthwhile loss (entirely below −δ), practically equivalent (entirely inside ±δ), or unresolved. One champion (the baseline can win); extra complexity only on a worthwhile gain; rationale in the stakeholder's terms (what the gain means, secondary checks, runner-up, what would change the decision). Fold wins are description only; no model's own interval, interval overlap, or lower bound picks the champion; the test set is not used to select.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13–21 pts: Plausible model; some tuning with partial documentation; CV present but thin; compares with the baseline on CV means or side-by-side intervals rather than paired per-fold differences; judges a winner or a tie by whether intervals overlap or by fold signs alone; calls the models equivalent when the interval extends past the margin; or states no margin; limited practical takeaways.</t>
+          <t>13–21 pts: Plausible model and tuning, but the comparison or decision is incomplete: folds not paired; δ missing, set after the results, or without business meaning; verdict from means, overlap, fold signs, or a model's own interval; unresolved called equivalent; or a champion without a rationale tied to the decision.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0–12 pts: Misaligned/unspecified model; superficial/absent tuning; incorrect CV; opaque selection; no clear comparison or interpretation.</t>
+          <t>0–12 pts: Misaligned/unspecified model; superficial/absent tuning; incorrect CV; no clear comparison and no justified champion.</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9–10 pts: Clear, scannable poster; logical flow (Intro→Methods→Results→Conclusions); legible, labeled figures/tables (titles, axes, units, legends); consistent typography/layout; code refs/appendix where appropriate; minimal grammar issues.</t>
+          <t>9–10 pts: Clear, scannable poster; logical flow (Intro→Methods→Results→Conclusions); the champion and its main reason are easy to find; legible, labeled figures/tables (titles, axes, units, legends); consistent typography/layout; code refs/appendix where appropriate; minimal grammar issues.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">

--- a/_final_project/2026F/rubric/Predictive_Analytics_Poster_Rubric.xlsx
+++ b/_final_project/2026F/rubric/Predictive_Analytics_Poster_Rubric.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22–25 pts: Model aligned to data/goal (e.g., RF/GBM/SVM/NN); tuning inside CV with leakage controls. Before comparing: primary metric, margin δ (smallest gain that would change the stakeholder's decision, with its business meaning), and candidate order (simplest first). Identical folds; per-fold differences (positive favors the challenger); interval corrected for fold overlap: mean ± t × SD(differences) × √(1/k + 1/(k−1)); outcome named: worthwhile gain (entirely above δ), worthwhile loss (entirely below −δ), practically equivalent (entirely inside ±δ), or unresolved. One champion (the baseline can win); extra complexity only on a worthwhile gain; rationale in the stakeholder's terms (what the gain means, secondary checks, runner-up, what would change the decision). Fold wins are description only; no model's own interval, interval overlap, or lower bound picks the champion; the test set is not used to select.</t>
+          <t>22–25 pts: Model aligned to data/goal (e.g., RF/GBM/SVM/NN); tuning inside CV with leakage controls. Before comparing: primary metric, margin δ (smallest gain that would change the stakeholder's decision, with its business meaning), and candidate order (simplest first). Identical folds; per-fold differences (positive favors the challenger); the verdict from a rule applied correctly: notebook 08's rule (Fall 2026 note) or, recommended, the interval corrected for fold overlap, mean ± t × SD(differences) × √(1/k + 1/(k−1)), named as worthwhile gain (entirely above δ), worthwhile loss (entirely below −δ), practically equivalent (entirely inside ±δ), or unresolved. One champion (the baseline can win); extra complexity only on a worthwhile gain; rationale in the stakeholder's terms (what the gain means, secondary checks, runner-up, what would change the decision). No model's own interval, interval overlap, or lower bound picks the champion; the test set is not used to select.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13–21 pts: Plausible model and tuning, but the comparison or decision is incomplete: folds not paired; δ missing, set after the results, or without business meaning; verdict from means, overlap, fold signs, or a model's own interval; unresolved called equivalent; or a champion without a rationale tied to the decision.</t>
+          <t>13–21 pts: Plausible model and tuning, but the comparison or decision is incomplete, or misapplies the rule the team used: folds not paired; δ missing, without business meaning, or set after the results without saying so; verdict from means alone, interval overlap, or a model's own interval; with the corrected interval, unresolved called equivalent; or a champion without a rationale tied to the decision.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/_final_project/2026F/rubric/Predictive_Analytics_Poster_Rubric.xlsx
+++ b/_final_project/2026F/rubric/Predictive_Analytics_Poster_Rubric.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>14–17 pts: Appropriate simple baseline (e.g., Linear/Logistic Regression), the incumbent any complex model must beat; pipeline is leakage-safe; k=5/10 CV (time-respecting for forecasting) with a primary metric chosen for the cost of errors; reports the fold scores with their mean and SD (no per-model confidence interval needed); summarizes implications and limitations; proposes concrete next steps.</t>
+          <t>14–17 pts: Appropriate simple baseline (e.g., Linear/Logistic Regression), the reference any complex model must beat; pipeline is leakage-safe; k=5/10 CV (time-respecting for forecasting) with a primary metric chosen for the cost of errors; reports the CV mean with its SD and approximate 95% interval, labeled descriptive (notebook 08); summarizes implications and limitations; proposes concrete next steps.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22–25 pts: Model aligned to data/goal (e.g., RF/GBM/SVM/NN); tuning inside CV with leakage controls. Before comparing: primary metric, margin δ (smallest gain that would change the stakeholder's decision, with its business meaning), and candidate order (simplest first). Identical folds; per-fold differences (positive favors the challenger); the verdict from a rule applied correctly: notebook 08's rule (Fall 2026 note) or, recommended, the interval corrected for fold overlap, mean ± t × SD(differences) × √(1/k + 1/(k−1)), named as worthwhile gain (entirely above δ), worthwhile loss (entirely below −δ), practically equivalent (entirely inside ±δ), or unresolved. One champion (the baseline can win); extra complexity only on a worthwhile gain; rationale in the stakeholder's terms (what the gain means, secondary checks, runner-up, what would change the decision). No model's own interval, interval overlap, or lower bound picks the champion; the test set is not used to select.</t>
+          <t>22–25 pts: Model aligned to data/goal (e.g., RF/GBM/SVM/NN); tuning inside CV with leakage controls. Before comparing: the primary metric and a practical margin (the smallest gain that would change the stakeholder's decision, with its business meaning). Baseline and tuned model (and any other finalist) compared on identical folds (same splitter and seed): per-fold paired differences and their mean, with the verdict named correctly under notebook 08's rule: real difference (every fold favors the same model and the mean gap clears the margin), no winner (the sign changes across folds), or practically equivalent (same sign but under the margin, so the simpler model wins). One champion, chosen as notebook 14 teaches (the baseline can win); extra complexity only on a real difference; rationale in the stakeholder's terms (what the gain means, secondary checks, runner-up). Interval overlap does not pick the champion; the test set is not used to select.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13–21 pts: Plausible model and tuning, but the comparison or decision is incomplete, or misapplies the rule the team used: folds not paired; δ missing, without business meaning, or set after the results without saying so; verdict from means alone, interval overlap, or a model's own interval; with the corrected interval, unresolved called equivalent; or a champion without a rationale tied to the decision.</t>
+          <t>13–21 pts: Plausible model and tuning, but the comparison or decision is incomplete or misapplied: folds not paired; margin missing, without business meaning, or set after the results without saying so; verdict from means alone or from whether two intervals overlap; fold signs that disagree read as a win; or a champion without a rationale tied to the decision.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
